--- a/astro-site/public/dl/plan-chef-privado-showcooking-eventos/calculadora-pricing-chef-privado-showcooking.xlsx
+++ b/astro-site/public/dl/plan-chef-privado-showcooking-eventos/calculadora-pricing-chef-privado-showcooking.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 ejemplos validados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Calculadora pricing'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'10 ejemplos validados'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -531,7 +534,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -557,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -726,6 +730,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -741,7 +746,7 @@
       </c>
       <c r="B17" s="7">
         <f>IF(B5="B2B", IF(B6&lt;8, 95, IF(B6&lt;20, 78, 68)), IF(B6&lt;6, 75, IF(B6&lt;12, 62, 52)))</f>
-        <v/>
+        <v>62.0</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -757,7 +762,7 @@
       </c>
       <c r="B18" s="9">
         <f>IF(B9="exclusivo",1.45,IF(B9="premium",1.20,1.00))</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
@@ -773,7 +778,7 @@
       </c>
       <c r="B19" s="9">
         <f>IF(B8="Showcooking",1.18,IF(B8="Cena ejecutiva",1.15,IF(B8="Cooking Class",1.22,1.00)))</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -789,7 +794,7 @@
       </c>
       <c r="B20" s="7">
         <f>IF(B12="sí",18,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -805,7 +810,7 @@
       </c>
       <c r="B21" s="9">
         <f>IF(B13="no",60,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -821,7 +826,7 @@
       </c>
       <c r="B22" s="9">
         <f>IF(B14="sí",120,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -837,7 +842,7 @@
       </c>
       <c r="B23" s="7">
         <f>B7*0.85*2</f>
-        <v/>
+        <v>30.599999999999998</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -853,7 +858,7 @@
       </c>
       <c r="B24" s="7">
         <f>B11*120</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -861,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -876,7 +882,7 @@
       </c>
       <c r="B27" s="11">
         <f>B17*B18*B19+B20</f>
-        <v/>
+        <v>74.39999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -887,7 +893,7 @@
       </c>
       <c r="B28" s="11">
         <f>B27*B6</f>
-        <v/>
+        <v>595.1999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -898,7 +904,7 @@
       </c>
       <c r="B29" s="11">
         <f>B21+B22+B23+B24</f>
-        <v/>
+        <v>30.599999999999998</v>
       </c>
     </row>
     <row r="30">
@@ -909,7 +915,7 @@
       </c>
       <c r="B30" s="12">
         <f>B28+B29</f>
-        <v/>
+        <v>625.8</v>
       </c>
     </row>
     <row r="31">
@@ -920,7 +926,7 @@
       </c>
       <c r="B31" s="11">
         <f>B30/B6</f>
-        <v/>
+        <v>78.225</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +937,7 @@
       </c>
       <c r="B32" s="13">
         <f>B30*0.4</f>
-        <v/>
+        <v>250.32</v>
       </c>
     </row>
     <row r="33">
@@ -942,7 +948,7 @@
       </c>
       <c r="B33" s="11">
         <f>B30*0.58</f>
-        <v/>
+        <v>362.96399999999994</v>
       </c>
     </row>
     <row r="34">
@@ -957,31 +963,40 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -989,7 +1004,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1018,6 +1033,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1382,9 +1398,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>